--- a/data/production/production_2026-W42.xlsx
+++ b/data/production/production_2026-W42.xlsx
@@ -483,31 +483,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AU-676289</t>
+          <t>HO-306770</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Victor Petrov</t>
+          <t>Olivia Delgado</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1955.43</v>
+        <v>1448.66</v>
       </c>
     </row>
     <row r="5">
@@ -516,22 +516,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AU-685766</t>
+          <t>HO-431115</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Marcus Ibsen</t>
+          <t>Maria Novak</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1682.82</v>
+        <v>3096.41</v>
       </c>
     </row>
     <row r="6">
@@ -549,64 +549,64 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CM-246802</t>
+          <t>HO-953359</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Adrian Okafor</t>
+          <t>Nora Ruiz</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8077.31</v>
+        <v>2768.18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CM-290167</t>
+          <t>AU-600326</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lena Quill</t>
+          <t>Victor Castillo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>new</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3970.44</v>
+        <v>1288.78</v>
       </c>
     </row>
     <row r="8">
@@ -615,17 +615,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aisha Bello</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AU-786837</t>
+          <t>AU-708483</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ivy Okafor</t>
+          <t>Victor Castillo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>954.09</v>
+        <v>1693.33</v>
       </c>
     </row>
     <row r="9">
@@ -648,31 +648,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HO-400384</t>
+          <t>AU-459720</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nora Ashby</t>
+          <t>Maria Ashby</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>new</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2625.71</v>
+        <v>1757.56</v>
       </c>
     </row>
     <row r="10">
@@ -681,31 +681,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HO-922041</t>
+          <t>AU-712931</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mila Novak</t>
+          <t>Clara Pryor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1580.45</v>
+        <v>2015.19</v>
       </c>
     </row>
     <row r="11">
@@ -714,22 +714,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LF-576849</t>
+          <t>AU-884311</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Marcus Novak</t>
+          <t>Maria Duarte</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Life </t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1029.96</v>
+        <v>1714.38</v>
       </c>
     </row>
     <row r="12">
@@ -747,31 +747,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AU-992819</t>
+          <t>CM-717506</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mila Novak</t>
+          <t>Owen Kowal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>2245.21</v>
+          <t xml:space="preserve">Renewal </t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>$5,883.07</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -780,22 +782,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>TOM BECKER</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HO-404771</t>
+          <t>AU-566236</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hugo Kowal</t>
+          <t>Sofia Pryor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -803,10 +805,8 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$2,271.44</t>
-        </is>
+      <c r="G13" t="n">
+        <v>1423.31</v>
       </c>
     </row>
     <row r="14">
@@ -820,59 +820,61 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AU-213844</t>
+          <t>LF-910827</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Maria Moreau</t>
+          <t>Theo Moreau</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1467.32</v>
+        <v>1898.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LF-598985</t>
+          <t>AU-119506</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mila Novak</t>
+          <t>Maria Ashby</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1750.47</v>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>$1,811.89</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -886,17 +888,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LF-917546</t>
+          <t>AU-608673</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Marcus Novak</t>
+          <t>Ivy Okafor</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -905,7 +907,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>765</v>
+        <v>1097.16</v>
       </c>
     </row>
     <row r="17">
@@ -914,22 +916,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grant Fowler </t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HO-470711</t>
+          <t>AU-728456</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Olivia Hartley</t>
+          <t>Leah Okafor</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -938,7 +940,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1474.82</v>
+        <v>970.67</v>
       </c>
     </row>
     <row r="18">
@@ -947,35 +949,65 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Aisha Bello</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HO-217217</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Zoe Marsh</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Home </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2634.33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Luis Ortega</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>HO-390119</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>James Moreau</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HO-835444</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Clara Pryor</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>2421.66</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n"/>
+      <c r="G19" t="n">
+        <v>1841.29</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -983,17 +1015,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HO-234443</t>
+          <t>HO-308672</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mila Novak</t>
+          <t>Nora Ruiz</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1007,59 +1039,59 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1804.09</v>
+        <v>3057.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LF-240384</t>
+          <t>HO-641721</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Grace Albright</t>
+          <t>Sofia Marsh</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1720.24</v>
+        <v>1917.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AU-904771</t>
+          <t>AU-305371</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Olivia Delgado</t>
+          <t>Theo Moreau</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1072,10 +1104,8 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>$1,896.28</t>
-        </is>
+      <c r="G22" t="n">
+        <v>2457.92</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1119,26 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AU-690525</t>
+          <t>HO-324661</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>James Moreau</t>
+          <t>Elena Novak</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>$1,564.15</t>
-        </is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2788.36</v>
       </c>
     </row>
     <row r="24">
@@ -1119,22 +1147,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HO-814703</t>
+          <t>AU-445599</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Grace Albright</t>
+          <t>James Whitfield</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1143,41 +1171,11 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2690.69</v>
+        <v>1945.62</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Maya Chen</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AU-572536</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Mila Tanaka</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>1190.25</v>
-      </c>
+      <c r="A25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1185,22 +1183,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HO-276831</t>
+          <t>AU-662757</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ivy Okafor</t>
+          <t>Victor Petrov</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1209,7 +1207,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2796.17</v>
+        <v>1562.35</v>
       </c>
     </row>
     <row r="27">
@@ -1218,22 +1216,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CM-595036</t>
+          <t>HO-645687</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ivy Hartley</t>
+          <t>James Whitfield</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1241,10 +1239,8 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>$8,922.45</t>
-        </is>
+      <c r="G27" t="n">
+        <v>1472.73</v>
       </c>
     </row>
     <row r="28">
@@ -1253,31 +1249,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LF-343007</t>
+          <t>AU-744918</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Adrian Okafor</t>
+          <t>Alma Ashby</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>676.8</v>
+        <v>2236.72</v>
       </c>
     </row>
     <row r="29">
@@ -1286,31 +1282,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tom Becker </t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AU-594312</t>
+          <t>CM-220569</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Clara Haines</t>
+          <t>Sofia Marsh</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1801.8</v>
+        <v>7233.72</v>
       </c>
     </row>
     <row r="30">
@@ -1324,26 +1320,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LF-725510</t>
+          <t>AU-149777</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Hugo Kowal</t>
+          <t>Caleb Whitfield</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t xml:space="preserve">Auto </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1251.08</v>
+        <v>2308.71</v>
       </c>
     </row>
     <row r="31">
@@ -1357,12 +1353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HO-310040</t>
+          <t>HO-130056</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Leah Novak</t>
+          <t>Maria Ashby</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1376,7 +1372,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1929.8</v>
+        <v>2116.69</v>
       </c>
     </row>
     <row r="32">
@@ -1390,12 +1386,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AU-420310</t>
+          <t>AU-193250</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Theo Moreau</t>
+          <t>Ruby Ferreira</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1405,13 +1401,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>$1,418.44</t>
-        </is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>2006.38</v>
       </c>
     </row>
     <row r="33">
@@ -1420,33 +1414,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HO-259797</t>
+          <t>AU-489611</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jonah Calloway</t>
+          <t>Owen Petrov</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>$1,741.92</t>
-        </is>
+          <t>renewal</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1215.51</v>
       </c>
     </row>
     <row r="34">
@@ -1460,7 +1452,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CM-906564</t>
+          <t>CM-492806</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1480,7 +1472,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>$6,926.38</t>
+          <t>$3,840.70</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1482,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tom Becker</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AU-817611</t>
+          <t>AU-434792</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Leah Okafor</t>
+          <t>Mila Tanaka</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1510,11 +1502,13 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>2189.39</v>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>$1,727.31</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1525,7 +1519,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>74792.06</v>
+        <v>71230.53999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1539,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1577,20 +1571,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AU-992819</t>
+          <t>HO-838103</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2258.44</v>
+        <v>2968</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
@@ -1602,16 +1596,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CM-290167</t>
+          <t>HO-306770</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3763.12</v>
+        <v>1303.98</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1627,7 +1621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HO-404771</t>
+          <t>HO-431115</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1636,7 +1630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2254.3</v>
+        <v>3133.35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1652,20 +1646,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HO-234443</t>
+          <t>AU-450590</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1794.79</v>
+        <v>1582.32</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1671,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HO-390119</t>
+          <t>HO-835444</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2445.76</v>
+        <v>1717.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1702,16 +1696,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AU-420310</t>
+          <t>HO-645687</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1438.11</v>
+        <v>1380.58</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1727,16 +1721,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CM-246802</t>
+          <t>AU-489611</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8081.64</v>
+        <v>1093.41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1747,25 +1741,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CM-906564</t>
+          <t>AU-308776</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6262.86</v>
+        <v>2016.44</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1771,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CM-595036</t>
+          <t>CM-717506</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1786,7 +1780,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8991.73</v>
+        <v>5527.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1797,21 +1791,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AU-594312</t>
+          <t>CM-492806</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1809.79</v>
+        <v>3893.91</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1827,16 +1821,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AU-904771</t>
+          <t>HO-308672</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1773.97</v>
+        <v>3020.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1847,46 +1841,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AU-502995</t>
+          <t>LF-910827</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>956.63</v>
+        <v>1901.05</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HO-400384</t>
+          <t>AU-149777</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2477.97</v>
+        <v>2065.52</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1897,46 +1891,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HO-788793</t>
+          <t>AU-566236</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1523.59</v>
+        <v>1276.43</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HO-922041</t>
+          <t>AU-434792</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1508.97</v>
+        <v>1742.27</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1947,12 +1941,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AU-685766</t>
+          <t>AU-119506</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1961,7 +1955,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1659.36</v>
+        <v>1792.74</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1972,25 +1966,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Aisha Bello</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HO-641721</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1870.89</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Renewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Grant Fowler</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LF-952646</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>2264.61</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Lost</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HO-324661</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2570.55</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Renewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Grant Fowler</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AU-305371</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2374.65</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
